--- a/parser/data/xlsx/model_selection.xlsx
+++ b/parser/data/xlsx/model_selection.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="record_1_problem_definition" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="record_2_problem_definition" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="record_3_problem_definition" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -503,4 +505,200 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>canonical_type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>unsupervised</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>training_mode</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>unsupervised</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>default_metrics</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>silhouette_score, davies_bouldin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>configuration_status</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rule_confidence</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>llm_confidence</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>canonical_type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>unsupervised</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>training_mode</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>unsupervised</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>default_metrics</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>silhouette_score, davies_bouldin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>configuration_status</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rule_confidence</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>llm_confidence</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>